--- a/output/graficos_dimensiones/comunal_i_ingr_a_2021_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2021_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:09</t>
+    <t xml:space="preserve">2026-09-09 23:03</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2021_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2021_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:03</t>
+    <t xml:space="preserve">2026-09-17 14:00</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2021_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2021_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:00</t>
+    <t xml:space="preserve">2026-09-23 12:29</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2021_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2021_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:29</t>
+    <t xml:space="preserve">2026-10-02 14:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2021_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2021_biobio.xlsx
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Arauco</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Angeles</t>
+    <t xml:space="preserve">Los Ángeles</t>
   </si>
   <si>
     <t xml:space="preserve">Nacimiento</t>
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Lebu</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Alamos</t>
+    <t xml:space="preserve">Los Álamos</t>
   </si>
   <si>
     <t xml:space="preserve">Quilleco</t>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 14:13</t>
+    <t xml:space="preserve">2026-10-04 08:50</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2021_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2021_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 08:50</t>
+    <t xml:space="preserve">2026-10-05 10:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -580,7 +580,7 @@
         <v>2021</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1073287.12</v>
+        <v>1073287.13</v>
       </c>
     </row>
     <row r="3">
@@ -886,7 +886,7 @@
         <v>2021</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>723718.12</v>
+        <v>723718.13</v>
       </c>
     </row>
     <row r="21">
@@ -920,7 +920,7 @@
         <v>2021</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>709501.62</v>
+        <v>709501.63</v>
       </c>
     </row>
     <row r="23">
@@ -988,7 +988,7 @@
         <v>2021</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>697973.12</v>
+        <v>697973.13</v>
       </c>
     </row>
     <row r="27">
